--- a/inventories/baseline/lci-Sal-de-Vida.xlsx
+++ b/inventories/baseline/lci-Sal-de-Vida.xlsx
@@ -798,7 +798,7 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-0.04307235758422602</v>
+        <v>-0.04307235758422603</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -849,7 +849,7 @@
         <v>30</v>
       </c>
       <c r="B29">
-        <v>0.2871490505615067</v>
+        <v>0.2871490505615068</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>3</v>
       </c>
       <c r="B58">
-        <v>0.6688504759664212</v>
+        <v>0.6619942407197513</v>
       </c>
       <c r="C58" t="s">
         <v>1</v>
@@ -1181,7 +1181,7 @@
         <v>39</v>
       </c>
       <c r="B59">
-        <v>0.1639369050419736</v>
+        <v>0.1725071991003109</v>
       </c>
       <c r="C59" t="s">
         <v>1</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="B60">
-        <v>0.04496288284895929</v>
+        <v>0.04731345258569727</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1215,7 +1215,7 @@
         <v>31</v>
       </c>
       <c r="B61">
-        <v>0.1672126189916053</v>
+        <v>0.1654985601799378</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -1330,7 +1330,7 @@
         <v>3</v>
       </c>
       <c r="B73">
-        <v>0.03344625071140695</v>
+        <v>0.03344625071140694</v>
       </c>
       <c r="C73" t="s">
         <v>1</v>
@@ -1347,7 +1347,7 @@
         <v>26</v>
       </c>
       <c r="B74">
-        <v>0.9581921866107413</v>
+        <v>0.9581921866107412</v>
       </c>
       <c r="C74" t="s">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="B75">
-        <v>0.179317666802284</v>
+        <v>0.1793176668022841</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1381,7 +1381,7 @@
         <v>31</v>
       </c>
       <c r="B76">
-        <v>0.008361562677851738</v>
+        <v>0.008361562677851736</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
@@ -1645,7 +1645,7 @@
         <v>38</v>
       </c>
       <c r="B102">
-        <v>7.434740762227065</v>
+        <v>7.511741933126094</v>
       </c>
       <c r="C102" t="s">
         <v>1</v>
@@ -1662,7 +1662,7 @@
         <v>22</v>
       </c>
       <c r="B103">
-        <v>0.008014231335733984</v>
+        <v>0.00809723425627191</v>
       </c>
       <c r="C103" t="s">
         <v>23</v>
@@ -1679,7 +1679,7 @@
         <v>42</v>
       </c>
       <c r="B104">
-        <v>-0.006434740762227065</v>
+        <v>-0.006511741933126094</v>
       </c>
       <c r="C104" t="s">
         <v>1</v>
@@ -2224,7 +2224,7 @@
         <v>48</v>
       </c>
       <c r="B157">
-        <v>0.0339999999889172</v>
+        <v>0.03197964184305711</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -2241,7 +2241,7 @@
         <v>49</v>
       </c>
       <c r="B158">
-        <v>1.915008683342068E-10</v>
+        <v>1.801214465870182E-10</v>
       </c>
       <c r="D158" t="s">
         <v>50</v>
@@ -2258,7 +2258,7 @@
         <v>52</v>
       </c>
       <c r="B159">
-        <v>4.787521708355171E-12</v>
+        <v>4.503036164675456E-12</v>
       </c>
       <c r="D159" t="s">
         <v>53</v>
@@ -2275,7 +2275,7 @@
         <v>54</v>
       </c>
       <c r="B160">
-        <v>4.787521708355171E-12</v>
+        <v>4.503036164675456E-12</v>
       </c>
       <c r="D160" t="s">
         <v>53</v>
@@ -2326,7 +2326,7 @@
         <v>3</v>
       </c>
       <c r="B163">
-        <v>0.1158336200137479</v>
+        <v>0.1683728185044284</v>
       </c>
       <c r="C163" t="s">
         <v>1</v>
@@ -2343,7 +2343,7 @@
         <v>55</v>
       </c>
       <c r="B164">
-        <v>9.503286701668942E-05</v>
+        <v>8.938579563244845E-05</v>
       </c>
       <c r="C164" t="s">
         <v>1</v>
@@ -2360,7 +2360,7 @@
         <v>22</v>
       </c>
       <c r="B165">
-        <v>0.03842213289648312</v>
+        <v>0.03614425125299725</v>
       </c>
       <c r="C165" t="s">
         <v>23</v>
@@ -2377,7 +2377,7 @@
         <v>57</v>
       </c>
       <c r="B166">
-        <v>1.01469790279671E-09</v>
+        <v>0.1849760250170622</v>
       </c>
       <c r="C166" t="s">
         <v>35</v>
@@ -2394,7 +2394,7 @@
         <v>58</v>
       </c>
       <c r="B167">
-        <v>0.0002085005154380095</v>
+        <v>0.0001961109355874648</v>
       </c>
       <c r="C167" t="s">
         <v>35</v>
@@ -2411,7 +2411,7 @@
         <v>59</v>
       </c>
       <c r="B168">
-        <v>-1.059612801958186E-16</v>
+        <v>-9.966481738231365E-17</v>
       </c>
       <c r="C168" t="s">
         <v>35</v>
@@ -2428,7 +2428,7 @@
         <v>42</v>
       </c>
       <c r="B169">
-        <v>-0.0001158336196877831</v>
+        <v>-0.0001089505197708138</v>
       </c>
       <c r="C169" t="s">
         <v>1</v>
@@ -2594,7 +2594,7 @@
         <v>3</v>
       </c>
       <c r="B184">
-        <v>0.825</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="C184" t="s">
         <v>1</v>
